--- a/Week 3/sales-data (1) (1).xlsx
+++ b/Week 3/sales-data (1) (1).xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jacly\OneDrive\Desktop\DataAnalyticsCourse\Jaclyn_Homework\Week 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730640C3-40F7-491F-A2BD-0610E0765630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB04B8C-3116-489A-8303-1AD382554C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2670" yWindow="150" windowWidth="22920" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$B$40</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>Product</t>
   </si>
@@ -105,9 +105,6 @@
     <t>Appliances</t>
   </si>
   <si>
-    <t>This Is A Shared File!!!! Make sure you follow the instrutions in the workshop to make a copy!!!!</t>
-  </si>
-  <si>
     <t>Blender</t>
   </si>
   <si>
@@ -140,12 +137,24 @@
   <si>
     <t>Correct</t>
   </si>
+  <si>
+    <t>Average Monthly Sales</t>
+  </si>
+  <si>
+    <t>Best Month</t>
+  </si>
+  <si>
+    <t>Worst Month</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,6 +175,13 @@
       <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -191,28 +207,81 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -223,6 +292,4766 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Category </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v> Laptop </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Smartphone </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Headphones </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Desk Chair </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v> Coffee Maker </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v> Blender </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v> T-Shirt </c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v> Jeans </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v> Sneakers </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4624-494C-ADE2-DC5AD6FBE39F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Jan Sales </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v> Laptop </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Smartphone </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Headphones </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Desk Chair </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v> Coffee Maker </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v> Blender </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v> T-Shirt </c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v> Jeans </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v> Sneakers </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4624-494C-ADE2-DC5AD6FBE39F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Feb Sales </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v> Laptop </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Smartphone </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Headphones </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Desk Chair </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v> Coffee Maker </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v> Blender </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v> T-Shirt </c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v> Jeans </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v> Sneakers </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3970</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4624-494C-ADE2-DC5AD6FBE39F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Mar Sales </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v> Laptop </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Smartphone </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Headphones </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Desk Chair </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v> Coffee Maker </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v> Blender </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v> T-Shirt </c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v> Jeans </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v> Sneakers </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1350</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4390</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4624-494C-ADE2-DC5AD6FBE39F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v> Laptop </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Smartphone </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Headphones </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Desk Chair </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v> Coffee Maker </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v> Blender </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v> T-Shirt </c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v> Jeans </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v> Sneakers </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$2:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3950</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2850</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11810</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-4624-494C-ADE2-DC5AD6FBE39F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1104824751"/>
+        <c:axId val="1851720655"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1104824751"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1851720655"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1851720655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1104824751"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="1"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:bar3DChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Category </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v> Laptop </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Smartphone </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Headphones </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Desk Chair </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v> Coffee Maker </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v> Blender </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v> T-Shirt </c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v> Jeans </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v> Sneakers </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-17BF-407C-AA97-11BFE31B8FCF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Jan Sales </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v> Laptop </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Smartphone </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Headphones </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Desk Chair </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v> Coffee Maker </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v> Blender </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v> T-Shirt </c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v> Jeans </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v> Sneakers </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-17BF-407C-AA97-11BFE31B8FCF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Feb Sales </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v> Laptop </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Smartphone </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Headphones </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Desk Chair </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v> Coffee Maker </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v> Blender </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v> T-Shirt </c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v> Jeans </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v> Sneakers </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3970</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-17BF-407C-AA97-11BFE31B8FCF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Mar Sales </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v> Laptop </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Smartphone </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Headphones </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Desk Chair </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v> Coffee Maker </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v> Blender </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v> T-Shirt </c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v> Jeans </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v> Sneakers </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$2:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1350</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4390</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-17BF-407C-AA97-11BFE31B8FCF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v> Laptop </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Smartphone </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Headphones </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Desk Chair </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v> Coffee Maker </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v> Blender </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v> T-Shirt </c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v> Jeans </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v> Sneakers </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$2:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3950</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2850</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11810</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-17BF-407C-AA97-11BFE31B8FCF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:shape val="box"/>
+        <c:axId val="1966059023"/>
+        <c:axId val="1851751375"/>
+        <c:axId val="0"/>
+      </c:bar3DChart>
+      <c:catAx>
+        <c:axId val="1966059023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1851751375"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1851751375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1966059023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> Laptop </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Electronics </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v> Jan Sales </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Feb Sales </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Mar Sales </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1350</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3950</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3998-4515-9FDF-B5F123555583}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$3:$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> Smartphone </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Electronics </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v> Jan Sales </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Feb Sales </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Mar Sales </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$3:$F$3</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2850</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3998-4515-9FDF-B5F123555583}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$4:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> Headphones </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Electronics </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v> Jan Sales </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Feb Sales </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Mar Sales </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>600</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3998-4515-9FDF-B5F123555583}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$5:$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> Desk Chair </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Furniture </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v> Jan Sales </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Feb Sales </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Mar Sales </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$5:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-3998-4515-9FDF-B5F123555583}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$6:$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> Coffee Maker </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Appliances </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v> Jan Sales </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Feb Sales </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Mar Sales </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>420</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-3998-4515-9FDF-B5F123555583}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$7:$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> Blender </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Appliances </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v> Jan Sales </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Feb Sales </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Mar Sales </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$7:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>290</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-3998-4515-9FDF-B5F123555583}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$8:$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> T-Shirt </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Clothing </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v> Jan Sales </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Feb Sales </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Mar Sales </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$8:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>750</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-3998-4515-9FDF-B5F123555583}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$9:$B$9</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> Jeans </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Clothing </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v> Jan Sales </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Feb Sales </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Mar Sales </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$9:$F$9</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1050</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-3998-4515-9FDF-B5F123555583}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$10:$B$10</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> Sneakers </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Footware </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v> Jan Sales </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Feb Sales </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Mar Sales </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$10:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>850</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-3998-4515-9FDF-B5F123555583}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$11:$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v> Jan Sales </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Feb Sales </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v> Mar Sales </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$11:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3970</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4390</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11810</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-3998-4515-9FDF-B5F123555583}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>73025</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>53975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1298575</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>60325</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E76F0158-8DEE-AF1E-A729-37281A3BA047}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1520825</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>73025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>34925</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A5314E8-116F-985F-8841-0A58B7D7AE84}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>301625</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>73025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>3044825</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDB69925-CE2E-B4F0-0635-878221C64081}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -542,18 +5371,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="57.88671875" customWidth="1"/>
+    <col min="1" max="1" width="28.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1796875" style="1" customWidth="1"/>
+    <col min="7" max="9" width="8.7265625" style="1"/>
+    <col min="10" max="10" width="57.90625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -573,234 +5405,349 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>1200</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>1400</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>1350</v>
       </c>
+      <c r="F2" s="1">
+        <f>SUM(C2:E2)</f>
+        <v>3950</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>800</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>950</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>1100</v>
       </c>
+      <c r="F3" s="1">
+        <f>SUM(C3:E3)</f>
+        <v>2850</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>150</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>200</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>250</v>
       </c>
+      <c r="F4" s="1">
+        <f>SUM(C4:E4)</f>
+        <v>600</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>350</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>300</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>400</v>
       </c>
+      <c r="F5" s="1">
+        <f>SUM(C5:E5)</f>
+        <v>1050</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>120</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>140</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>160</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="F6" s="1">
+        <f>SUM(C6:E6)</f>
+        <v>420</v>
+      </c>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1">
+        <v>80</v>
+      </c>
+      <c r="D7" s="1">
+        <v>100</v>
+      </c>
+      <c r="E7" s="1">
+        <v>110</v>
+      </c>
+      <c r="F7" s="1">
+        <f>SUM(C7:E7)</f>
+        <v>290</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7">
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1">
+        <v>200</v>
+      </c>
+      <c r="D8" s="1">
+        <v>250</v>
+      </c>
+      <c r="E8" s="1">
+        <v>300</v>
+      </c>
+      <c r="F8" s="1">
+        <f>SUM(C8:E8)</f>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1">
+        <v>300</v>
+      </c>
+      <c r="D9" s="1">
+        <v>350</v>
+      </c>
+      <c r="E9" s="1">
+        <v>400</v>
+      </c>
+      <c r="F9" s="1">
+        <f>SUM(C9:E9)</f>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1">
+        <v>250</v>
+      </c>
+      <c r="D10" s="1">
+        <v>280</v>
+      </c>
+      <c r="E10" s="1">
+        <v>320</v>
+      </c>
+      <c r="F10" s="1">
+        <f>SUM(C10:E10)</f>
+        <v>850</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <f>SUM(C2:C10)</f>
+        <v>3450</v>
+      </c>
+      <c r="D11" s="1">
+        <f>SUM(D2:D10)</f>
+        <v>3970</v>
+      </c>
+      <c r="E11" s="1">
+        <f>SUM(E2:E10)</f>
+        <v>4390</v>
+      </c>
+      <c r="F11" s="1">
+        <f>SUM(F2:F10)</f>
+        <v>11810</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1">
+        <f>AVERAGE(C2:E10)</f>
+        <v>437.40740740740739</v>
+      </c>
+      <c r="C13" s="1">
+        <f>AVERAGE(D2:D10)</f>
+        <v>441.11111111111109</v>
+      </c>
+      <c r="D13" s="1">
+        <f>AVERAGE(E2:E10)</f>
+        <v>487.77777777777777</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="1">
+        <f>MAX(C2:E10)</f>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="1">
+        <f>MIN(C2:E10)</f>
         <v>80</v>
       </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>110</v>
-      </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8">
-        <v>200</v>
-      </c>
-      <c r="D8">
-        <v>250</v>
-      </c>
-      <c r="E8">
-        <v>300</v>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>300</v>
-      </c>
-      <c r="D9">
-        <v>350</v>
-      </c>
-      <c r="E9">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10">
-        <v>250</v>
-      </c>
-      <c r="D10">
-        <v>280</v>
-      </c>
-      <c r="E10">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
         <f>MAX(C2:E2)</f>
         <v>1400</v>
       </c>
-      <c r="C15" t="str">
-        <f ca="1">+_xlfn.FORMULATEXT(A15)</f>
-        <v>=MAX(C2:E2)</v>
+      <c r="D18" s="1">
+        <f>MAX(C2:E2)</f>
+        <v>1400</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+    <row r="20" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="5"/>
+    </row>
+    <row r="21" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" cm="1">
+        <f t="array" ref="A21">MAX(_xlfn._xlws.FILTER(C2:E10, B2:B10="Electronics"))</f>
+        <v>1400</v>
+      </c>
+      <c r="D21" s="1" cm="1">
+        <f t="array" ref="D21">MAX(_xlfn._xlws.FILTER(C2:E10,B2:B10="Electronics"))</f>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="4"/>
     </row>
-    <row r="18" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" cm="1">
-        <f t="array" ref="A18">MAX(_xlfn._xlws.FILTER(C2:E10, B2:B10="Electronics"))</f>
-        <v>1400</v>
-      </c>
-      <c r="C18" t="str">
-        <f ca="1">+_xlfn.FORMULATEXT(A18)</f>
-        <v>=MAX(FILTER(C2:E10, B2:B10="Electronics"))</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="1">
         <f>MAX(SUMIF(B2:B10, "Electronics", C2:E10))</f>
         <v>2150</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" t="str">
-        <f ca="1">+_xlfn.FORMULATEXT(A21)</f>
+      <c r="B24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="1" t="str">
+        <f ca="1">+_xlfn.FORMULATEXT(A24)</f>
         <v>=MAX(SUMIF(B2:B10, "Electronics", C2:E10))</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
         <f>SUMIF($B$2:$B$10, "Electronics", C$2:C$10)</f>
         <v>2150</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" t="str">
-        <f ca="1">+_xlfn.FORMULATEXT(A22)</f>
+      <c r="B25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="1" t="str">
+        <f ca="1">+_xlfn.FORMULATEXT(A25)</f>
         <v>=SUMIF($B$2:$B$10, "Electronics", C$2:C$10)</v>
       </c>
+      <c r="D25" s="1">
+        <f>SUMIF($B$2:$B$10, "Electronics", C$2:C$10)</f>
+        <v>2150</v>
+      </c>
     </row>
-    <row r="24" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="19.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
+  <conditionalFormatting sqref="A1:G11">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="top10" dxfId="3" priority="3" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:F11">
+    <cfRule type="top10" dxfId="0" priority="2" rank="10"/>
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>